--- a/2VAR_ATSBS_T2W/2var_atsbs_p50_t2w_PUBLICTR.xlsx
+++ b/2VAR_ATSBS_T2W/2var_atsbs_p50_t2w_PUBLICTR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/philliao/Downloads/Code/IB-Math-IA/2VAR_ATSBS_T2W/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77DCE96D-B863-5741-9592-BD3209560D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C51B9AAA-5A3E-5B48-AF8A-2D1F5BF0CC91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="25600" windowHeight="16000" xr2:uid="{2EA0D6E5-C2F1-7748-A0B4-904626257646}"/>
   </bookViews>
@@ -16,10 +16,7 @@
     <sheet name="Regression" sheetId="1" r:id="rId1"/>
     <sheet name="Outlier" sheetId="2" r:id="rId2"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId3"/>
-  </externalReferences>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="30">
   <si>
     <t>district_name</t>
   </si>
@@ -59,12 +56,87 @@
   <si>
     <t>r value</t>
   </si>
+  <si>
+    <t>SUMMARY OUTPUT</t>
+  </si>
+  <si>
+    <t>Regression Statistics</t>
+  </si>
+  <si>
+    <t>Multiple R</t>
+  </si>
+  <si>
+    <t>R Square</t>
+  </si>
+  <si>
+    <t>Adjusted R Square</t>
+  </si>
+  <si>
+    <t>Standard Error</t>
+  </si>
+  <si>
+    <t>Observations</t>
+  </si>
+  <si>
+    <t>ANOVA</t>
+  </si>
+  <si>
+    <t>Regression</t>
+  </si>
+  <si>
+    <t>Residual</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Intercept</t>
+  </si>
+  <si>
+    <t>df</t>
+  </si>
+  <si>
+    <t>SS</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Significance F</t>
+  </si>
+  <si>
+    <t>Coefficients</t>
+  </si>
+  <si>
+    <t>t Stat</t>
+  </si>
+  <si>
+    <t>P-value</t>
+  </si>
+  <si>
+    <t>Lower 95%</t>
+  </si>
+  <si>
+    <t>Upper 95%</t>
+  </si>
+  <si>
+    <t>Lower 95.0%</t>
+  </si>
+  <si>
+    <t>Upper 95.0%</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="0.000%"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -84,6 +156,21 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -93,7 +180,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -101,17 +188,51 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -615,6 +736,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -622,7 +744,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -814,7 +935,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Regression!$C$18:$C$29</c:f>
+              <c:f>Regression!$Q$2:$Q$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -838,7 +959,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Regression!$B$18:$B$29</c:f>
+              <c:f>Regression!$P$2:$P$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -1122,6 +1243,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1129,7 +1251,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1321,7 +1442,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Regression!$C$34:$C$45</c:f>
+              <c:f>Regression!$AE$2:$AE$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -1342,7 +1463,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Regression!$B$34:$B$45</c:f>
+              <c:f>Regression!$AD$2:$AD$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -1623,6 +1744,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1630,7 +1752,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3375,15 +3496,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>806450</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3413,15 +3534,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
+      <xdr:col>37</xdr:col>
       <xdr:colOff>806450</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3450,19 +3571,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Regression"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3782,10 +3890,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E21254B-8104-CD4E-940B-61592D463C14}">
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:AO35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3795,8 +3903,26 @@
       <c r="C1" t="s">
         <v>3</v>
       </c>
+      <c r="O1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -3806,8 +3932,22 @@
       <c r="C2" s="2">
         <v>2.1459359999999998</v>
       </c>
+      <c r="O2" s="1">
+        <v>1</v>
+      </c>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="2"/>
+      <c r="AC2" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD2" s="1">
+        <v>-0.20784630000000001</v>
+      </c>
+      <c r="AE2" s="2">
+        <v>2.1459359999999998</v>
+      </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -3817,8 +3957,22 @@
       <c r="C3" s="2">
         <v>0.74672099999999997</v>
       </c>
+      <c r="O3" s="1">
+        <v>2</v>
+      </c>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="2"/>
+      <c r="AC3" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD3" s="1">
+        <v>-0.13281899999999999</v>
+      </c>
+      <c r="AE3" s="2">
+        <v>0.74672099999999997</v>
+      </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -3835,13 +3989,47 @@
         <f>CORREL(C2:C13,B2:B13)</f>
         <v>-0.22715162053090265</v>
       </c>
+      <c r="O4" s="1">
+        <v>3</v>
+      </c>
+      <c r="P4" s="1">
+        <v>-0.14957390000000001</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>2.266483</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z4">
+        <f>CORREL(Q2:Q13,P2:P13)</f>
+        <v>-0.29909597890974204</v>
+      </c>
+      <c r="AC4" s="1">
+        <v>3</v>
+      </c>
+      <c r="AD4" s="1"/>
+      <c r="AE4" s="2"/>
+      <c r="AM4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN4">
+        <f>CORREL(AE2:AE13,AD2:AD13)</f>
+        <v>-0.99630288460261185</v>
+      </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
+      <c r="O5" s="1">
+        <v>4</v>
+      </c>
+      <c r="AC5" s="1">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -3851,13 +4039,33 @@
       <c r="C6" s="2">
         <v>3.1496979999999999</v>
       </c>
+      <c r="O6" s="1">
+        <v>5</v>
+      </c>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="2"/>
+      <c r="AC6" s="1">
+        <v>5</v>
+      </c>
+      <c r="AD6" s="1">
+        <v>-0.2662949</v>
+      </c>
+      <c r="AE6" s="2">
+        <v>3.1496979999999999</v>
+      </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
+      <c r="O7" s="1">
+        <v>6</v>
+      </c>
+      <c r="AC7" s="1">
+        <v>6</v>
+      </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -3867,8 +4075,22 @@
       <c r="C8" s="2">
         <v>4.7154689999999997</v>
       </c>
+      <c r="O8" s="1">
+        <v>7</v>
+      </c>
+      <c r="P8" s="1">
+        <v>-0.14164119999999999</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>4.7154689999999997</v>
+      </c>
+      <c r="AC8" s="1">
+        <v>7</v>
+      </c>
+      <c r="AD8" s="1"/>
+      <c r="AE8" s="2"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -3878,13 +4100,33 @@
       <c r="C9" s="2">
         <v>1.595407</v>
       </c>
+      <c r="O9" s="1">
+        <v>8</v>
+      </c>
+      <c r="P9" s="1">
+        <v>-0.13194539999999999</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>1.595407</v>
+      </c>
+      <c r="AC9" s="1">
+        <v>8</v>
+      </c>
+      <c r="AD9" s="1"/>
+      <c r="AE9" s="2"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>9</v>
       </c>
+      <c r="O10" s="1">
+        <v>9</v>
+      </c>
+      <c r="AC10" s="1">
+        <v>9</v>
+      </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -3894,8 +4136,22 @@
       <c r="C11" s="2">
         <v>1.3538140000000001</v>
       </c>
+      <c r="O11" s="1">
+        <v>10</v>
+      </c>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="2"/>
+      <c r="AC11" s="1">
+        <v>10</v>
+      </c>
+      <c r="AD11" s="1">
+        <v>-0.15528020000000001</v>
+      </c>
+      <c r="AE11" s="2">
+        <v>1.3538140000000001</v>
+      </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -3905,8 +4161,22 @@
       <c r="C12" s="2">
         <v>3.1974629999999999</v>
       </c>
+      <c r="O12" s="1">
+        <v>11</v>
+      </c>
+      <c r="P12" s="1">
+        <v>-0.15887780000000001</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>3.1974629999999999</v>
+      </c>
+      <c r="AC12" s="1">
+        <v>11</v>
+      </c>
+      <c r="AD12" s="1"/>
+      <c r="AE12" s="2"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -3916,234 +4186,800 @@
       <c r="C13" s="2">
         <v>2.4929640000000002</v>
       </c>
+      <c r="O13" s="1">
+        <v>12</v>
+      </c>
+      <c r="P13" s="1">
+        <v>-0.137266</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>2.4929640000000002</v>
+      </c>
+      <c r="AC13" s="1">
+        <v>12</v>
+      </c>
+      <c r="AD13" s="1"/>
+      <c r="AE13" s="2"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B18" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C18" t="s">
         <v>3</v>
       </c>
+      <c r="E18" t="s">
+        <v>6</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" s="1">
+    <row r="19" spans="1:38" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
         <v>1</v>
       </c>
-      <c r="B18" s="1"/>
-      <c r="C18" s="2"/>
+      <c r="B19" s="1">
+        <v>-0.20784630000000001</v>
+      </c>
+      <c r="C19" s="2">
+        <v>2.1459359999999998</v>
+      </c>
+      <c r="O19" s="1">
+        <v>3</v>
+      </c>
+      <c r="P19" s="1">
+        <v>-0.14957390000000001</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>2.266483</v>
+      </c>
+      <c r="AC19" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD19" s="1">
+        <v>-0.20784630000000001</v>
+      </c>
+      <c r="AE19" s="2">
+        <v>2.1459359999999998</v>
+      </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A19" s="1">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
         <v>2</v>
       </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="2"/>
+      <c r="B20" s="1">
+        <v>-0.13281899999999999</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0.74672099999999997</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" s="6"/>
+      <c r="O20" s="1">
+        <v>7</v>
+      </c>
+      <c r="P20" s="1">
+        <v>-0.14164119999999999</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>4.7154689999999997</v>
+      </c>
+      <c r="S20" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="T20" s="6"/>
+      <c r="AC20" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD20" s="1">
+        <v>-0.13281899999999999</v>
+      </c>
+      <c r="AE20" s="2">
+        <v>0.74672099999999997</v>
+      </c>
+      <c r="AG20" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH20" s="6"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A20" s="1">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
         <v>3</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B21" s="1">
         <v>-0.14957390000000001</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C21" s="2">
         <v>2.266483</v>
       </c>
-      <c r="K20" t="s">
+      <c r="E21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="3">
+        <v>0.22715162053090265</v>
+      </c>
+      <c r="O21" s="1">
+        <v>8</v>
+      </c>
+      <c r="P21" s="1">
+        <v>-0.13194539999999999</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>1.595407</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T21" s="3">
+        <v>0.29909597890974171</v>
+      </c>
+      <c r="AC21" s="1">
         <v>5</v>
       </c>
-      <c r="L20">
-        <f>CORREL(C18:C29,B18:B29)</f>
-        <v>-0.29909597890974204</v>
+      <c r="AD21" s="1">
+        <v>-0.2662949</v>
+      </c>
+      <c r="AE21" s="2">
+        <v>3.1496979999999999</v>
+      </c>
+      <c r="AG21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH21" s="3">
+        <v>0.99630288460261196</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>5</v>
       </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="2"/>
+      <c r="B22" s="1">
+        <v>-0.2662949</v>
+      </c>
+      <c r="C22" s="2">
+        <v>3.1496979999999999</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="3">
+        <v>5.1597858709815196E-2</v>
+      </c>
+      <c r="O22" s="1">
+        <v>11</v>
+      </c>
+      <c r="P22" s="1">
+        <v>-0.15887780000000001</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>3.1974629999999999</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="T22" s="3">
+        <v>8.9458404599976671E-2</v>
+      </c>
+      <c r="AC22" s="1">
+        <v>10</v>
+      </c>
+      <c r="AD22" s="1">
+        <v>-0.15528020000000001</v>
+      </c>
+      <c r="AE22" s="2">
+        <v>1.3538140000000001</v>
+      </c>
+      <c r="AG22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>0.99261943786748552</v>
+      </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="B23" s="1">
+        <v>-0.14164119999999999</v>
+      </c>
+      <c r="C23" s="2">
+        <v>4.7154689999999997</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="3">
+        <v>-8.3888161474496917E-2</v>
+      </c>
+      <c r="O23" s="1">
+        <v>12</v>
+      </c>
+      <c r="P23" s="1">
+        <v>-0.137266</v>
+      </c>
+      <c r="Q23" s="2">
+        <v>2.4929640000000002</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T23" s="3">
+        <v>-0.21405546053336444</v>
+      </c>
+      <c r="AG23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH23" s="3">
+        <v>0.98892915680122828</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
+        <v>8</v>
+      </c>
+      <c r="B24" s="1">
+        <v>-0.13194539999999999</v>
+      </c>
+      <c r="C24" s="2">
+        <v>1.595407</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="3">
+        <v>4.6425461618224813E-2</v>
+      </c>
+      <c r="O24" s="1"/>
+      <c r="S24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="T24" s="3">
+        <v>1.1667883090226358E-2</v>
+      </c>
+      <c r="AC24" s="1"/>
+      <c r="AG24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AH24" s="3">
+        <v>6.2582730143978605E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:38" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>10</v>
+      </c>
+      <c r="B25" s="1">
+        <v>-0.15528020000000001</v>
+      </c>
+      <c r="C25" s="2">
+        <v>1.3538140000000001</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="4">
+        <v>9</v>
+      </c>
+      <c r="S25" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="T25" s="4">
+        <v>5</v>
+      </c>
+      <c r="AC25" s="1"/>
+      <c r="AD25" s="1"/>
+      <c r="AE25" s="2"/>
+      <c r="AG25" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="AH25" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>11</v>
+      </c>
+      <c r="B26" s="1">
+        <v>-0.15887780000000001</v>
+      </c>
+      <c r="C26" s="2">
+        <v>3.1974629999999999</v>
+      </c>
+      <c r="AC26" s="1"/>
+      <c r="AD26" s="1"/>
+      <c r="AE26" s="2"/>
+    </row>
+    <row r="27" spans="1:38" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>12</v>
+      </c>
+      <c r="B27" s="1">
+        <v>-0.137266</v>
+      </c>
+      <c r="C27" s="2">
+        <v>2.4929640000000002</v>
+      </c>
+      <c r="E27" t="s">
+        <v>13</v>
+      </c>
+      <c r="O27" s="1"/>
+      <c r="S27" t="s">
+        <v>13</v>
+      </c>
+      <c r="AC27" s="1"/>
+      <c r="AG27" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="E28" s="5"/>
+      <c r="F28" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="2"/>
+      <c r="S28" s="5"/>
+      <c r="T28" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="U28" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="V28" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="W28" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="X28" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="AG28" s="5"/>
+      <c r="AH28" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="AI28" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="AJ28" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="AK28" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AL28" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="E29" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29" s="3">
+        <v>1</v>
+      </c>
+      <c r="G29" s="3">
+        <v>8.2082325967869872E-4</v>
+      </c>
+      <c r="H29" s="3">
+        <v>8.2082325967869872E-4</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0.38083529680495914</v>
+      </c>
+      <c r="J29" s="7">
+        <v>0.55668877430334274</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="T29" s="3">
+        <v>1</v>
+      </c>
+      <c r="U29" s="3">
+        <v>4.0126081530430222E-5</v>
+      </c>
+      <c r="V29" s="3">
+        <v>4.0126081530430222E-5</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0.29474239854141554</v>
+      </c>
+      <c r="X29" s="7">
+        <v>0.62493584601264751</v>
+      </c>
+      <c r="AC29" s="1"/>
+      <c r="AD29" s="1"/>
+      <c r="AE29" s="2"/>
+      <c r="AG29" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>1</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>1.0534946652454521E-2</v>
+      </c>
+      <c r="AJ29" s="3">
+        <v>1.0534946652454521E-2</v>
+      </c>
+      <c r="AK29" s="3">
+        <v>268.98206939944976</v>
+      </c>
+      <c r="AL29" s="9">
+        <v>3.6971153973880612E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="E30" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F30" s="3">
         <v>7</v>
       </c>
-      <c r="B24" s="1">
-        <v>-0.14164119999999999</v>
-      </c>
-      <c r="C24" s="2">
-        <v>4.7154689999999997</v>
-      </c>
+      <c r="G30" s="3">
+        <v>1.5087264405256857E-2</v>
+      </c>
+      <c r="H30" s="3">
+        <v>2.1553234864652654E-3</v>
+      </c>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="S30" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="T30" s="3">
+        <v>3</v>
+      </c>
+      <c r="U30" s="3">
+        <v>4.0841848742157057E-4</v>
+      </c>
+      <c r="V30" s="3">
+        <v>1.3613949580719019E-4</v>
+      </c>
+      <c r="W30" s="3"/>
+      <c r="X30" s="3"/>
+      <c r="AC30" s="1"/>
+      <c r="AD30" s="1"/>
+      <c r="AE30" s="2"/>
+      <c r="AG30" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>2</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>7.8331962245480974E-5</v>
+      </c>
+      <c r="AJ30" s="3">
+        <v>3.9165981122740487E-5</v>
+      </c>
+      <c r="AK30" s="3"/>
+      <c r="AL30" s="3"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A25" s="1">
+    <row r="31" spans="1:38" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E31" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" s="4">
         <v>8</v>
       </c>
-      <c r="B25" s="1">
-        <v>-0.13194539999999999</v>
-      </c>
-      <c r="C25" s="2">
-        <v>1.595407</v>
-      </c>
+      <c r="G31" s="4">
+        <v>1.5908087664935556E-2</v>
+      </c>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="S31" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="T31" s="4">
+        <v>4</v>
+      </c>
+      <c r="U31" s="4">
+        <v>4.4854456895200079E-4</v>
+      </c>
+      <c r="V31" s="4"/>
+      <c r="W31" s="4"/>
+      <c r="X31" s="4"/>
+      <c r="AG31" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH31" s="4">
+        <v>3</v>
+      </c>
+      <c r="AI31" s="4">
+        <v>1.0613278614700001E-2</v>
+      </c>
+      <c r="AJ31" s="4"/>
+      <c r="AK31" s="4"/>
+      <c r="AL31" s="4"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" s="1">
-        <v>9</v>
+    <row r="32" spans="1:38" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="5:41" x14ac:dyDescent="0.2">
+      <c r="E33" s="5"/>
+      <c r="F33" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L33" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M33" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="S33" s="5"/>
+      <c r="T33" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="U33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="V33" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="W33" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="X33" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y33" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z33" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA33" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="AG33" s="5"/>
+      <c r="AH33" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="AI33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AJ33" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="AK33" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL33" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM33" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN33" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="AO33" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" s="1">
-        <v>10</v>
-      </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="2"/>
+    <row r="34" spans="5:41" x14ac:dyDescent="0.2">
+      <c r="E34" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F34" s="3">
+        <v>-0.14394005903390117</v>
+      </c>
+      <c r="G34" s="3">
+        <v>3.6905378848464912E-2</v>
+      </c>
+      <c r="H34" s="3">
+        <v>-3.9002460759155273</v>
+      </c>
+      <c r="I34" s="7">
+        <v>5.8970099951857228E-3</v>
+      </c>
+      <c r="J34" s="3">
+        <v>-0.23120741287320071</v>
+      </c>
+      <c r="K34" s="3">
+        <v>-5.667270519460163E-2</v>
+      </c>
+      <c r="L34" s="3">
+        <v>-0.23120741287320071</v>
+      </c>
+      <c r="M34" s="3">
+        <v>-5.667270519460163E-2</v>
+      </c>
+      <c r="S34" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="T34" s="3">
+        <v>-0.13625129459006693</v>
+      </c>
+      <c r="U34" s="3">
+        <v>1.4956244057155704E-2</v>
+      </c>
+      <c r="V34" s="3">
+        <v>-9.109994064644761</v>
+      </c>
+      <c r="W34" s="7">
+        <v>2.7950622756653188E-3</v>
+      </c>
+      <c r="X34" s="3">
+        <v>-0.18384873823068354</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>-8.865385094945033E-2</v>
+      </c>
+      <c r="Z34" s="3">
+        <v>-0.18384873823068354</v>
+      </c>
+      <c r="AA34" s="3">
+        <v>-8.865385094945033E-2</v>
+      </c>
+      <c r="AG34" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>-8.5127205689266988E-2</v>
+      </c>
+      <c r="AI34" s="3">
+        <v>7.1496869827029986E-3</v>
+      </c>
+      <c r="AJ34" s="3">
+        <v>-11.90642414069489</v>
+      </c>
+      <c r="AK34" s="9">
+        <v>6.9802577892959803E-3</v>
+      </c>
+      <c r="AL34" s="3">
+        <v>-0.11588982590224825</v>
+      </c>
+      <c r="AM34" s="3">
+        <v>-5.4364585476285726E-2</v>
+      </c>
+      <c r="AN34" s="3">
+        <v>-0.11588982590224825</v>
+      </c>
+      <c r="AO34" s="3">
+        <v>-5.4364585476285726E-2</v>
+      </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A28" s="1">
-        <v>11</v>
-      </c>
-      <c r="B28" s="1">
-        <v>-0.15887780000000001</v>
-      </c>
-      <c r="C28" s="2">
-        <v>3.1974629999999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A29" s="1">
-        <v>12</v>
-      </c>
-      <c r="B29" s="1">
-        <v>-0.137266</v>
-      </c>
-      <c r="C29" s="2">
-        <v>2.4929640000000002</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A33" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C33" t="s">
+    <row r="35" spans="5:41" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E35" s="4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A34" s="1">
-        <v>1</v>
-      </c>
-      <c r="B34" s="1">
-        <v>-0.20784630000000001</v>
-      </c>
-      <c r="C34" s="2">
-        <v>2.1459359999999998</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A35" s="1">
-        <v>2</v>
-      </c>
-      <c r="B35" s="1">
-        <v>-0.13281899999999999</v>
-      </c>
-      <c r="C35" s="2">
-        <v>0.74672099999999997</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A36" s="1">
+      <c r="F35" s="4">
+        <v>-8.5895751119723623E-3</v>
+      </c>
+      <c r="G35" s="4">
+        <v>1.3918841366244947E-2</v>
+      </c>
+      <c r="H35" s="4">
+        <v>-0.61711854355946838</v>
+      </c>
+      <c r="I35" s="8">
+        <v>0.55668877430334274</v>
+      </c>
+      <c r="J35" s="4">
+        <v>-4.1502404960668017E-2</v>
+      </c>
+      <c r="K35" s="4">
+        <v>2.4323254736723292E-2</v>
+      </c>
+      <c r="L35" s="4">
+        <v>-4.1502404960668017E-2</v>
+      </c>
+      <c r="M35" s="4">
+        <v>2.4323254736723292E-2</v>
+      </c>
+      <c r="S35" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B36" s="1"/>
-      <c r="C36" s="2"/>
-      <c r="K36" t="s">
-        <v>5</v>
-      </c>
-      <c r="L36">
-        <f>CORREL(C34:C45,B34:B45)</f>
-        <v>-0.99630288460261185</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A37" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A38" s="1">
-        <v>5</v>
-      </c>
-      <c r="B38" s="1">
-        <v>-0.2662949</v>
-      </c>
-      <c r="C38" s="2">
-        <v>3.1496979999999999</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A39" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A40" s="1">
-        <v>7</v>
-      </c>
-      <c r="B40" s="1"/>
-      <c r="C40" s="2"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A41" s="1">
-        <v>8</v>
-      </c>
-      <c r="B41" s="1"/>
-      <c r="C41" s="2"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A42" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A43" s="1">
-        <v>10</v>
-      </c>
-      <c r="B43" s="1">
-        <v>-0.15528020000000001</v>
-      </c>
-      <c r="C43" s="2">
-        <v>1.3538140000000001</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A44" s="1">
-        <v>11</v>
-      </c>
-      <c r="B44" s="1"/>
-      <c r="C44" s="2"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A45" s="1">
-        <v>12</v>
-      </c>
-      <c r="B45" s="1"/>
-      <c r="C45" s="2"/>
+      <c r="T35" s="4">
+        <v>-2.6666945417926332E-3</v>
+      </c>
+      <c r="U35" s="4">
+        <v>4.911927695837941E-3</v>
+      </c>
+      <c r="V35" s="4">
+        <v>-0.54290183140363046</v>
+      </c>
+      <c r="W35" s="8">
+        <v>0.62493584601264729</v>
+      </c>
+      <c r="X35" s="4">
+        <v>-1.8298640689232811E-2</v>
+      </c>
+      <c r="Y35" s="4">
+        <v>1.2965251605647545E-2</v>
+      </c>
+      <c r="Z35" s="4">
+        <v>-1.8298640689232811E-2</v>
+      </c>
+      <c r="AA35" s="4">
+        <v>1.2965251605647545E-2</v>
+      </c>
+      <c r="AG35" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH35" s="4">
+        <v>-5.7020273231037866E-2</v>
+      </c>
+      <c r="AI35" s="4">
+        <v>3.4767032919360594E-3</v>
+      </c>
+      <c r="AJ35" s="4">
+        <v>-16.400672833742217</v>
+      </c>
+      <c r="AK35" s="10">
+        <v>3.697115397388059E-3</v>
+      </c>
+      <c r="AL35" s="4">
+        <v>-7.1979320140615505E-2</v>
+      </c>
+      <c r="AM35" s="4">
+        <v>-4.2061226321460234E-2</v>
+      </c>
+      <c r="AN35" s="4">
+        <v>-7.1979320140615505E-2</v>
+      </c>
+      <c r="AO35" s="4">
+        <v>-4.2061226321460234E-2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/2VAR_ATSBS_T2W/2var_atsbs_p50_t2w_PUBLICTR.xlsx
+++ b/2VAR_ATSBS_T2W/2var_atsbs_p50_t2w_PUBLICTR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/philliao/Downloads/Code/IB-Math-IA/2VAR_ATSBS_T2W/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C51B9AAA-5A3E-5B48-AF8A-2D1F5BF0CC91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CADC1563-7DBA-6245-95B4-5D329A0BFC20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="25600" windowHeight="16000" xr2:uid="{2EA0D6E5-C2F1-7748-A0B4-904626257646}"/>
+    <workbookView xWindow="3840" yWindow="660" windowWidth="21760" windowHeight="14320" xr2:uid="{2EA0D6E5-C2F1-7748-A0B4-904626257646}"/>
   </bookViews>
   <sheets>
     <sheet name="Regression" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="33">
   <si>
     <t>district_name</t>
   </si>
@@ -128,13 +128,22 @@
   <si>
     <t>Upper 95.0%</t>
   </si>
+  <si>
+    <t>p50_acr_rank</t>
+  </si>
+  <si>
+    <t>rho=</t>
+  </si>
+  <si>
+    <t>Percent PUBLICTR rank</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.000%"/>
+    <numFmt numFmtId="164" formatCode="0.000%"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -213,22 +222,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -282,13 +290,8 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Congestion</a:t>
+              <a:t>ATSBS PUBLICTR</a:t>
             </a:r>
-            <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
-              <a:t> rate to public transportation usage</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -813,11 +816,11 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Congestion</a:t>
+              <a:t>ATSBS PUBLICTR </a:t>
             </a:r>
             <a:r>
               <a:rPr lang="en-US" baseline="0"/>
-              <a:t> rate to public transportation usage (Crowded)</a:t>
+              <a:t>(Crowded)</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -3890,7 +3893,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E21254B-8104-CD4E-940B-61592D463C14}">
-  <dimension ref="A1:AO35"/>
+  <dimension ref="A1:AO48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:40" x14ac:dyDescent="0.2">
@@ -4278,10 +4281,10 @@
       <c r="C20" s="2">
         <v>0.74672099999999997</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F20" s="6"/>
+      <c r="F20" s="5"/>
       <c r="O20" s="1">
         <v>7</v>
       </c>
@@ -4291,10 +4294,10 @@
       <c r="Q20" s="2">
         <v>4.7154689999999997</v>
       </c>
-      <c r="S20" s="6" t="s">
+      <c r="S20" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="T20" s="6"/>
+      <c r="T20" s="5"/>
       <c r="AC20" s="1">
         <v>2</v>
       </c>
@@ -4304,10 +4307,10 @@
       <c r="AE20" s="2">
         <v>0.74672099999999997</v>
       </c>
-      <c r="AG20" s="6" t="s">
+      <c r="AG20" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="AH20" s="6"/>
+      <c r="AH20" s="5"/>
     </row>
     <row r="21" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
@@ -4319,10 +4322,10 @@
       <c r="C21" s="2">
         <v>2.266483</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" t="s">
         <v>8</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21">
         <v>0.22715162053090265</v>
       </c>
       <c r="O21" s="1">
@@ -4334,10 +4337,10 @@
       <c r="Q21" s="2">
         <v>1.595407</v>
       </c>
-      <c r="S21" s="3" t="s">
+      <c r="S21" t="s">
         <v>8</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21">
         <v>0.29909597890974171</v>
       </c>
       <c r="AC21" s="1">
@@ -4349,10 +4352,10 @@
       <c r="AE21" s="2">
         <v>3.1496979999999999</v>
       </c>
-      <c r="AG21" s="3" t="s">
+      <c r="AG21" t="s">
         <v>8</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AH21">
         <v>0.99630288460261196</v>
       </c>
     </row>
@@ -4366,10 +4369,10 @@
       <c r="C22" s="2">
         <v>3.1496979999999999</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" t="s">
         <v>9</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22">
         <v>5.1597858709815196E-2</v>
       </c>
       <c r="O22" s="1">
@@ -4381,10 +4384,10 @@
       <c r="Q22" s="2">
         <v>3.1974629999999999</v>
       </c>
-      <c r="S22" s="3" t="s">
+      <c r="S22" t="s">
         <v>9</v>
       </c>
-      <c r="T22" s="3">
+      <c r="T22">
         <v>8.9458404599976671E-2</v>
       </c>
       <c r="AC22" s="1">
@@ -4396,10 +4399,10 @@
       <c r="AE22" s="2">
         <v>1.3538140000000001</v>
       </c>
-      <c r="AG22" s="3" t="s">
+      <c r="AG22" t="s">
         <v>9</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AH22">
         <v>0.99261943786748552</v>
       </c>
     </row>
@@ -4413,10 +4416,10 @@
       <c r="C23" s="2">
         <v>4.7154689999999997</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" t="s">
         <v>10</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23">
         <v>-8.3888161474496917E-2</v>
       </c>
       <c r="O23" s="1">
@@ -4428,16 +4431,16 @@
       <c r="Q23" s="2">
         <v>2.4929640000000002</v>
       </c>
-      <c r="S23" s="3" t="s">
+      <c r="S23" t="s">
         <v>10</v>
       </c>
-      <c r="T23" s="3">
+      <c r="T23">
         <v>-0.21405546053336444</v>
       </c>
-      <c r="AG23" s="3" t="s">
+      <c r="AG23" t="s">
         <v>10</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AH23">
         <v>0.98892915680122828</v>
       </c>
     </row>
@@ -4451,24 +4454,24 @@
       <c r="C24" s="2">
         <v>1.595407</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E24" t="s">
         <v>11</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24">
         <v>4.6425461618224813E-2</v>
       </c>
       <c r="O24" s="1"/>
-      <c r="S24" s="3" t="s">
+      <c r="S24" t="s">
         <v>11</v>
       </c>
-      <c r="T24" s="3">
+      <c r="T24">
         <v>1.1667883090226358E-2</v>
       </c>
       <c r="AC24" s="1"/>
-      <c r="AG24" s="3" t="s">
+      <c r="AG24" t="s">
         <v>11</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AH24">
         <v>6.2582730143978605E-3</v>
       </c>
     </row>
@@ -4482,25 +4485,25 @@
       <c r="C25" s="2">
         <v>1.3538140000000001</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F25" s="3">
         <v>9</v>
       </c>
-      <c r="S25" s="4" t="s">
+      <c r="S25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="T25" s="4">
+      <c r="T25" s="3">
         <v>5</v>
       </c>
       <c r="AC25" s="1"/>
       <c r="AD25" s="1"/>
       <c r="AE25" s="2"/>
-      <c r="AG25" s="4" t="s">
+      <c r="AG25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="AH25" s="4">
+      <c r="AH25" s="3">
         <v>4</v>
       </c>
     </row>
@@ -4541,448 +4544,832 @@
       </c>
     </row>
     <row r="28" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="E28" s="5"/>
-      <c r="F28" s="5" t="s">
+      <c r="E28" s="4"/>
+      <c r="F28" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="G28" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H28" s="5" t="s">
+      <c r="H28" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I28" s="5" t="s">
+      <c r="I28" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="J28" s="5" t="s">
+      <c r="J28" s="4" t="s">
         <v>22</v>
       </c>
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
       <c r="Q28" s="2"/>
-      <c r="S28" s="5"/>
-      <c r="T28" s="5" t="s">
+      <c r="S28" s="4"/>
+      <c r="T28" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="U28" s="5" t="s">
+      <c r="U28" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="V28" s="5" t="s">
+      <c r="V28" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="W28" s="5" t="s">
+      <c r="W28" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="X28" s="5" t="s">
+      <c r="X28" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="AG28" s="5"/>
-      <c r="AH28" s="5" t="s">
+      <c r="AG28" s="4"/>
+      <c r="AH28" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AI28" s="5" t="s">
+      <c r="AI28" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="AJ28" s="5" t="s">
+      <c r="AJ28" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="AK28" s="5" t="s">
+      <c r="AK28" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AL28" s="5" t="s">
+      <c r="AL28" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="E29" s="3" t="s">
+      <c r="E29" t="s">
         <v>14</v>
       </c>
-      <c r="F29" s="3">
+      <c r="F29">
         <v>1</v>
       </c>
-      <c r="G29" s="3">
+      <c r="G29">
         <v>8.2082325967869872E-4</v>
       </c>
-      <c r="H29" s="3">
+      <c r="H29">
         <v>8.2082325967869872E-4</v>
       </c>
-      <c r="I29" s="3">
+      <c r="I29">
         <v>0.38083529680495914</v>
       </c>
-      <c r="J29" s="7">
+      <c r="J29" s="6">
         <v>0.55668877430334274</v>
       </c>
-      <c r="S29" s="3" t="s">
+      <c r="S29" t="s">
         <v>14</v>
       </c>
-      <c r="T29" s="3">
+      <c r="T29">
         <v>1</v>
       </c>
-      <c r="U29" s="3">
+      <c r="U29">
         <v>4.0126081530430222E-5</v>
       </c>
-      <c r="V29" s="3">
+      <c r="V29">
         <v>4.0126081530430222E-5</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29">
         <v>0.29474239854141554</v>
       </c>
-      <c r="X29" s="7">
+      <c r="X29" s="6">
         <v>0.62493584601264751</v>
       </c>
       <c r="AC29" s="1"/>
       <c r="AD29" s="1"/>
       <c r="AE29" s="2"/>
-      <c r="AG29" s="3" t="s">
+      <c r="AG29" t="s">
         <v>14</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AH29">
         <v>1</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29">
         <v>1.0534946652454521E-2</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29">
         <v>1.0534946652454521E-2</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29">
         <v>268.98206939944976</v>
       </c>
-      <c r="AL29" s="9">
+      <c r="AL29" s="8">
         <v>3.6971153973880612E-3</v>
       </c>
     </row>
     <row r="30" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="E30" s="3" t="s">
+      <c r="E30" t="s">
         <v>15</v>
       </c>
-      <c r="F30" s="3">
+      <c r="F30">
         <v>7</v>
       </c>
-      <c r="G30" s="3">
+      <c r="G30">
         <v>1.5087264405256857E-2</v>
       </c>
-      <c r="H30" s="3">
+      <c r="H30">
         <v>2.1553234864652654E-3</v>
       </c>
-      <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
-      <c r="S30" s="3" t="s">
+      <c r="S30" t="s">
         <v>15</v>
       </c>
-      <c r="T30" s="3">
+      <c r="T30">
         <v>3</v>
       </c>
-      <c r="U30" s="3">
+      <c r="U30">
         <v>4.0841848742157057E-4</v>
       </c>
-      <c r="V30" s="3">
+      <c r="V30">
         <v>1.3613949580719019E-4</v>
       </c>
-      <c r="W30" s="3"/>
-      <c r="X30" s="3"/>
       <c r="AC30" s="1"/>
       <c r="AD30" s="1"/>
       <c r="AE30" s="2"/>
-      <c r="AG30" s="3" t="s">
+      <c r="AG30" t="s">
         <v>15</v>
       </c>
-      <c r="AH30" s="3">
+      <c r="AH30">
         <v>2</v>
       </c>
-      <c r="AI30" s="3">
+      <c r="AI30">
         <v>7.8331962245480974E-5</v>
       </c>
-      <c r="AJ30" s="3">
+      <c r="AJ30">
         <v>3.9165981122740487E-5</v>
       </c>
-      <c r="AK30" s="3"/>
-      <c r="AL30" s="3"/>
     </row>
     <row r="31" spans="1:38" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F31" s="3">
         <v>8</v>
       </c>
-      <c r="G31" s="4">
+      <c r="G31" s="3">
         <v>1.5908087664935556E-2</v>
       </c>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
-      <c r="S31" s="4" t="s">
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="S31" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T31" s="4">
+      <c r="T31" s="3">
         <v>4</v>
       </c>
-      <c r="U31" s="4">
+      <c r="U31" s="3">
         <v>4.4854456895200079E-4</v>
       </c>
-      <c r="V31" s="4"/>
-      <c r="W31" s="4"/>
-      <c r="X31" s="4"/>
-      <c r="AG31" s="4" t="s">
+      <c r="V31" s="3"/>
+      <c r="W31" s="3"/>
+      <c r="X31" s="3"/>
+      <c r="AG31" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AH31" s="4">
+      <c r="AH31" s="3">
         <v>3</v>
       </c>
-      <c r="AI31" s="4">
+      <c r="AI31" s="3">
         <v>1.0613278614700001E-2</v>
       </c>
-      <c r="AJ31" s="4"/>
-      <c r="AK31" s="4"/>
-      <c r="AL31" s="4"/>
+      <c r="AJ31" s="3"/>
+      <c r="AK31" s="3"/>
+      <c r="AL31" s="3"/>
     </row>
     <row r="32" spans="1:38" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="5:41" x14ac:dyDescent="0.2">
-      <c r="E33" s="5"/>
-      <c r="F33" s="5" t="s">
+    <row r="33" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="E33" s="4"/>
+      <c r="F33" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G33" s="5" t="s">
+      <c r="G33" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H33" s="5" t="s">
+      <c r="H33" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I33" s="5" t="s">
+      <c r="I33" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="J33" s="5" t="s">
+      <c r="J33" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="K33" s="5" t="s">
+      <c r="K33" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="L33" s="5" t="s">
+      <c r="L33" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M33" s="5" t="s">
+      <c r="M33" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="S33" s="5"/>
-      <c r="T33" s="5" t="s">
+      <c r="S33" s="4"/>
+      <c r="T33" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="U33" s="5" t="s">
+      <c r="U33" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="V33" s="5" t="s">
+      <c r="V33" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="W33" s="5" t="s">
+      <c r="W33" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="X33" s="5" t="s">
+      <c r="X33" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="Y33" s="5" t="s">
+      <c r="Y33" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="Z33" s="5" t="s">
+      <c r="Z33" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="AA33" s="5" t="s">
+      <c r="AA33" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="AG33" s="5"/>
-      <c r="AH33" s="5" t="s">
+      <c r="AG33" s="4"/>
+      <c r="AH33" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="AI33" s="5" t="s">
+      <c r="AI33" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="AJ33" s="5" t="s">
+      <c r="AJ33" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AK33" s="5" t="s">
+      <c r="AK33" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="AL33" s="5" t="s">
+      <c r="AL33" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="AM33" s="5" t="s">
+      <c r="AM33" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="AN33" s="5" t="s">
+      <c r="AN33" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="AO33" s="5" t="s">
+      <c r="AO33" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="34" spans="5:41" x14ac:dyDescent="0.2">
-      <c r="E34" s="3" t="s">
+    <row r="34" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="E34" t="s">
         <v>17</v>
       </c>
-      <c r="F34" s="3">
+      <c r="F34">
         <v>-0.14394005903390117</v>
       </c>
-      <c r="G34" s="3">
+      <c r="G34">
         <v>3.6905378848464912E-2</v>
       </c>
-      <c r="H34" s="3">
+      <c r="H34">
         <v>-3.9002460759155273</v>
       </c>
-      <c r="I34" s="7">
+      <c r="I34" s="6">
         <v>5.8970099951857228E-3</v>
       </c>
-      <c r="J34" s="3">
+      <c r="J34">
         <v>-0.23120741287320071</v>
       </c>
-      <c r="K34" s="3">
+      <c r="K34">
         <v>-5.667270519460163E-2</v>
       </c>
-      <c r="L34" s="3">
+      <c r="L34">
         <v>-0.23120741287320071</v>
       </c>
-      <c r="M34" s="3">
+      <c r="M34">
         <v>-5.667270519460163E-2</v>
       </c>
-      <c r="S34" s="3" t="s">
+      <c r="S34" t="s">
         <v>17</v>
       </c>
-      <c r="T34" s="3">
+      <c r="T34">
         <v>-0.13625129459006693</v>
       </c>
-      <c r="U34" s="3">
+      <c r="U34">
         <v>1.4956244057155704E-2</v>
       </c>
-      <c r="V34" s="3">
+      <c r="V34">
         <v>-9.109994064644761</v>
       </c>
-      <c r="W34" s="7">
+      <c r="W34" s="6">
         <v>2.7950622756653188E-3</v>
       </c>
-      <c r="X34" s="3">
+      <c r="X34">
         <v>-0.18384873823068354</v>
       </c>
-      <c r="Y34" s="3">
+      <c r="Y34">
         <v>-8.865385094945033E-2</v>
       </c>
-      <c r="Z34" s="3">
+      <c r="Z34">
         <v>-0.18384873823068354</v>
       </c>
-      <c r="AA34" s="3">
+      <c r="AA34">
         <v>-8.865385094945033E-2</v>
       </c>
-      <c r="AG34" s="3" t="s">
+      <c r="AG34" t="s">
         <v>17</v>
       </c>
-      <c r="AH34" s="3">
+      <c r="AH34">
         <v>-8.5127205689266988E-2</v>
       </c>
-      <c r="AI34" s="3">
+      <c r="AI34">
         <v>7.1496869827029986E-3</v>
       </c>
-      <c r="AJ34" s="3">
+      <c r="AJ34">
         <v>-11.90642414069489</v>
       </c>
-      <c r="AK34" s="9">
+      <c r="AK34" s="8">
         <v>6.9802577892959803E-3</v>
       </c>
-      <c r="AL34" s="3">
+      <c r="AL34">
         <v>-0.11588982590224825</v>
       </c>
-      <c r="AM34" s="3">
+      <c r="AM34">
         <v>-5.4364585476285726E-2</v>
       </c>
-      <c r="AN34" s="3">
+      <c r="AN34">
         <v>-0.11588982590224825</v>
       </c>
-      <c r="AO34" s="3">
+      <c r="AO34">
         <v>-5.4364585476285726E-2</v>
       </c>
     </row>
-    <row r="35" spans="5:41" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E35" s="4" t="s">
+    <row r="35" spans="1:41" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F35" s="4">
+      <c r="F35" s="3">
         <v>-8.5895751119723623E-3</v>
       </c>
-      <c r="G35" s="4">
+      <c r="G35" s="3">
         <v>1.3918841366244947E-2</v>
       </c>
-      <c r="H35" s="4">
+      <c r="H35" s="3">
         <v>-0.61711854355946838</v>
       </c>
-      <c r="I35" s="8">
+      <c r="I35" s="7">
         <v>0.55668877430334274</v>
       </c>
-      <c r="J35" s="4">
+      <c r="J35" s="3">
         <v>-4.1502404960668017E-2</v>
       </c>
-      <c r="K35" s="4">
+      <c r="K35" s="3">
         <v>2.4323254736723292E-2</v>
       </c>
-      <c r="L35" s="4">
+      <c r="L35" s="3">
         <v>-4.1502404960668017E-2</v>
       </c>
-      <c r="M35" s="4">
+      <c r="M35" s="3">
         <v>2.4323254736723292E-2</v>
       </c>
-      <c r="S35" s="4" t="s">
+      <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T35" s="4">
+      <c r="T35" s="3">
         <v>-2.6666945417926332E-3</v>
       </c>
-      <c r="U35" s="4">
+      <c r="U35" s="3">
         <v>4.911927695837941E-3</v>
       </c>
-      <c r="V35" s="4">
+      <c r="V35" s="3">
         <v>-0.54290183140363046</v>
       </c>
-      <c r="W35" s="8">
+      <c r="W35" s="7">
         <v>0.62493584601264729</v>
       </c>
-      <c r="X35" s="4">
+      <c r="X35" s="3">
         <v>-1.8298640689232811E-2</v>
       </c>
-      <c r="Y35" s="4">
+      <c r="Y35" s="3">
         <v>1.2965251605647545E-2</v>
       </c>
-      <c r="Z35" s="4">
+      <c r="Z35" s="3">
         <v>-1.8298640689232811E-2</v>
       </c>
-      <c r="AA35" s="4">
+      <c r="AA35" s="3">
         <v>1.2965251605647545E-2</v>
       </c>
-      <c r="AG35" s="4" t="s">
+      <c r="AG35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AH35" s="4">
+      <c r="AH35" s="3">
         <v>-5.7020273231037866E-2</v>
       </c>
-      <c r="AI35" s="4">
+      <c r="AI35" s="3">
         <v>3.4767032919360594E-3</v>
       </c>
-      <c r="AJ35" s="4">
+      <c r="AJ35" s="3">
         <v>-16.400672833742217</v>
       </c>
-      <c r="AK35" s="10">
+      <c r="AK35" s="9">
         <v>3.697115397388059E-3</v>
       </c>
-      <c r="AL35" s="4">
+      <c r="AL35" s="3">
         <v>-7.1979320140615505E-2</v>
       </c>
-      <c r="AM35" s="4">
+      <c r="AM35" s="3">
         <v>-4.2061226321460234E-2</v>
       </c>
-      <c r="AN35" s="4">
+      <c r="AN35" s="3">
         <v>-7.1979320140615505E-2</v>
       </c>
-      <c r="AO35" s="4">
+      <c r="AO35" s="3">
         <v>-4.2061226321460234E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D39" t="s">
+        <v>3</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>30</v>
+      </c>
+      <c r="R39" t="s">
+        <v>3</v>
+      </c>
+      <c r="S39" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE39" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF39" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG39" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="40" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>1</v>
+      </c>
+      <c r="B40" s="1">
+        <v>-0.20784630000000001</v>
+      </c>
+      <c r="C40">
+        <f>_xlfn.RANK.AVG(B40,B$40:B$48,1)</f>
+        <v>2</v>
+      </c>
+      <c r="D40" s="2">
+        <v>2.1459359999999998</v>
+      </c>
+      <c r="E40">
+        <f>_xlfn.RANK.AVG(D40,D$40:D$48,1)</f>
+        <v>4</v>
+      </c>
+      <c r="G40" t="s">
+        <v>31</v>
+      </c>
+      <c r="H40">
+        <f>CORREL(C40:C48,E40:E48)</f>
+        <v>-0.36666666666666675</v>
+      </c>
+      <c r="O40" s="1">
+        <v>3</v>
+      </c>
+      <c r="P40" s="1">
+        <v>-0.14957390000000001</v>
+      </c>
+      <c r="Q40">
+        <f>_xlfn.RANK.AVG(P40,P$40:P$44,1)</f>
+        <v>2</v>
+      </c>
+      <c r="R40" s="2">
+        <v>2.266483</v>
+      </c>
+      <c r="S40">
+        <f>_xlfn.RANK.AVG(R40,R$40:R$44,1)</f>
+        <v>2</v>
+      </c>
+      <c r="U40" t="s">
+        <v>31</v>
+      </c>
+      <c r="V40">
+        <f>CORREL(Q40:Q44,S40:S44)</f>
+        <v>-0.49999999999999989</v>
+      </c>
+      <c r="AC40" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD40" s="1">
+        <v>-0.20784630000000001</v>
+      </c>
+      <c r="AE40">
+        <f>_xlfn.RANK.AVG(AD40,AD$40:AD$43,1)</f>
+        <v>2</v>
+      </c>
+      <c r="AF40" s="2">
+        <v>2.1459359999999998</v>
+      </c>
+      <c r="AG40">
+        <f>_xlfn.RANK.AVG(AF40,AF$40:AF$43,1)</f>
+        <v>3</v>
+      </c>
+      <c r="AI40" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ40">
+        <f>CORREL(AE40:AE43,AG40:AG43)</f>
+        <v>-0.99999999999999978</v>
+      </c>
+    </row>
+    <row r="41" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
+        <v>2</v>
+      </c>
+      <c r="B41" s="1">
+        <v>-0.13281899999999999</v>
+      </c>
+      <c r="C41">
+        <f t="shared" ref="C41:C48" si="0">_xlfn.RANK.AVG(B41,B$40:B$48,1)</f>
+        <v>8</v>
+      </c>
+      <c r="D41" s="2">
+        <v>0.74672099999999997</v>
+      </c>
+      <c r="E41">
+        <f t="shared" ref="E41:E48" si="1">_xlfn.RANK.AVG(D41,D$40:D$48,1)</f>
+        <v>1</v>
+      </c>
+      <c r="O41" s="1">
+        <v>7</v>
+      </c>
+      <c r="P41" s="1">
+        <v>-0.14164119999999999</v>
+      </c>
+      <c r="Q41">
+        <f t="shared" ref="Q41:Q44" si="2">_xlfn.RANK.AVG(P41,P$40:P$44,1)</f>
+        <v>3</v>
+      </c>
+      <c r="R41" s="2">
+        <v>4.7154689999999997</v>
+      </c>
+      <c r="S41">
+        <f t="shared" ref="S41:S44" si="3">_xlfn.RANK.AVG(R41,R$40:R$44,1)</f>
+        <v>5</v>
+      </c>
+      <c r="AC41" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD41" s="1">
+        <v>-0.13281899999999999</v>
+      </c>
+      <c r="AE41">
+        <f t="shared" ref="AE41:AE43" si="4">_xlfn.RANK.AVG(AD41,AD$40:AD$43,1)</f>
+        <v>4</v>
+      </c>
+      <c r="AF41" s="2">
+        <v>0.74672099999999997</v>
+      </c>
+      <c r="AG41">
+        <f t="shared" ref="AG41:AG43" si="5">_xlfn.RANK.AVG(AF41,AF$40:AF$43,1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
+        <v>3</v>
+      </c>
+      <c r="B42" s="1">
+        <v>-0.14957390000000001</v>
+      </c>
+      <c r="C42">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="D42" s="2">
+        <v>2.266483</v>
+      </c>
+      <c r="E42">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="O42" s="1">
+        <v>8</v>
+      </c>
+      <c r="P42" s="1">
+        <v>-0.13194539999999999</v>
+      </c>
+      <c r="Q42">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="R42" s="2">
+        <v>1.595407</v>
+      </c>
+      <c r="S42">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AC42" s="1">
+        <v>5</v>
+      </c>
+      <c r="AD42" s="1">
+        <v>-0.2662949</v>
+      </c>
+      <c r="AE42">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AF42" s="2">
+        <v>3.1496979999999999</v>
+      </c>
+      <c r="AG42">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
+        <v>5</v>
+      </c>
+      <c r="B43" s="1">
+        <v>-0.2662949</v>
+      </c>
+      <c r="C43">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D43" s="2">
+        <v>3.1496979999999999</v>
+      </c>
+      <c r="E43">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="O43" s="1">
+        <v>11</v>
+      </c>
+      <c r="P43" s="1">
+        <v>-0.15887780000000001</v>
+      </c>
+      <c r="Q43">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="R43" s="2">
+        <v>3.1974629999999999</v>
+      </c>
+      <c r="S43">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="AC43" s="1">
+        <v>10</v>
+      </c>
+      <c r="AD43" s="1">
+        <v>-0.15528020000000001</v>
+      </c>
+      <c r="AE43">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="AF43" s="2">
+        <v>1.3538140000000001</v>
+      </c>
+      <c r="AG43">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A44" s="1">
+        <v>7</v>
+      </c>
+      <c r="B44" s="1">
+        <v>-0.14164119999999999</v>
+      </c>
+      <c r="C44">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="D44" s="2">
+        <v>4.7154689999999997</v>
+      </c>
+      <c r="E44">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="O44" s="1">
+        <v>12</v>
+      </c>
+      <c r="P44" s="1">
+        <v>-0.137266</v>
+      </c>
+      <c r="Q44">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="R44" s="2">
+        <v>2.4929640000000002</v>
+      </c>
+      <c r="S44">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A45" s="1">
+        <v>8</v>
+      </c>
+      <c r="B45" s="1">
+        <v>-0.13194539999999999</v>
+      </c>
+      <c r="C45">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="D45" s="2">
+        <v>1.595407</v>
+      </c>
+      <c r="E45">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A46" s="1">
+        <v>10</v>
+      </c>
+      <c r="B46" s="1">
+        <v>-0.15528020000000001</v>
+      </c>
+      <c r="C46">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="D46" s="2">
+        <v>1.3538140000000001</v>
+      </c>
+      <c r="E46">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A47" s="1">
+        <v>11</v>
+      </c>
+      <c r="B47" s="1">
+        <v>-0.15887780000000001</v>
+      </c>
+      <c r="C47">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="D47" s="2">
+        <v>3.1974629999999999</v>
+      </c>
+      <c r="E47">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A48" s="1">
+        <v>12</v>
+      </c>
+      <c r="B48" s="1">
+        <v>-0.137266</v>
+      </c>
+      <c r="C48">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="D48" s="2">
+        <v>2.4929640000000002</v>
+      </c>
+      <c r="E48">
+        <f t="shared" si="1"/>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>

--- a/2VAR_ATSBS_T2W/2var_atsbs_p50_t2w_PUBLICTR.xlsx
+++ b/2VAR_ATSBS_T2W/2var_atsbs_p50_t2w_PUBLICTR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/philliao/Downloads/Code/IB-Math-IA/2VAR_ATSBS_T2W/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CADC1563-7DBA-6245-95B4-5D329A0BFC20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48D71F7C-8E3A-494F-81A2-2B14E84B7DB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3840" yWindow="660" windowWidth="21760" windowHeight="14320" xr2:uid="{2EA0D6E5-C2F1-7748-A0B4-904626257646}"/>
   </bookViews>
@@ -142,8 +142,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000%"/>
+    <numFmt numFmtId="171" formatCode="0.000"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -222,7 +223,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -237,6 +238,7 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3895,6 +3897,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E21254B-8104-CD4E-940B-61592D463C14}">
   <dimension ref="A1:AO48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -5043,7 +5048,7 @@
       <c r="G40" t="s">
         <v>31</v>
       </c>
-      <c r="H40">
+      <c r="H40" s="10">
         <f>CORREL(C40:C48,E40:E48)</f>
         <v>-0.36666666666666675</v>
       </c>
